--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MICHIGAN_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MICHIGAN_2017.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C82">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C120">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C216">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C533">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C581">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C600">
